--- a/V9_W8_B32/data_instructions/VLIW_Excel/Unit13_2_DownSamplingR.xlsx
+++ b/V9_W8_B32/data_instructions/VLIW_Excel/Unit13_2_DownSamplingR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V7\data_instructions\VLIW_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V9_W8_B32\data_instructions\VLIW_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A679EA9B-4952-42E5-81A4-F4A908381888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4D6326-EDA1-441D-B62C-B66AA63B3005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{427F1CDB-5AAB-483C-A031-4C1182026265}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{427F1CDB-5AAB-483C-A031-4C1182026265}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="91">
   <si>
     <t>OP_Code</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -398,6 +398,10 @@
   </si>
   <si>
     <t>010600_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Requant_Sel[3]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -645,10 +649,37 @@
     <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -660,34 +691,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1153,23 +1157,26 @@
       <c r="M5" s="8" t="s">
         <v>81</v>
       </c>
+      <c r="N5" s="7" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
+      <c r="D7" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="21"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
       <c r="L7" s="9" t="s">
         <v>0</v>
       </c>
@@ -1195,14 +1202,14 @@
       <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
       <c r="L8" s="11" t="s">
         <v>5</v>
       </c>
@@ -1241,14 +1248,14 @@
       <c r="A9">
         <v>0</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
       <c r="L9" s="12" t="s">
         <v>15</v>
       </c>
@@ -1265,14 +1272,14 @@
       <c r="U9" s="10"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C10" s="17"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
       <c r="L10" s="14" t="s">
         <v>17</v>
       </c>
@@ -1296,14 +1303,14 @@
       <c r="U10" s="10"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C11" s="17"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
       <c r="L11" s="15" t="s">
         <v>23</v>
       </c>
@@ -1325,22 +1332,22 @@
       <c r="B12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
+      <c r="E12" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
       <c r="L12" s="9" t="s">
         <v>0</v>
       </c>
@@ -1366,14 +1373,14 @@
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
       <c r="L13" s="11" t="s">
         <v>5</v>
       </c>
@@ -1409,14 +1416,14 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C14" s="17"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
       <c r="L14" s="12" t="s">
         <v>15</v>
       </c>
@@ -1442,14 +1449,14 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
       <c r="L15" s="14" t="s">
         <v>17</v>
       </c>
@@ -1472,14 +1479,14 @@
       <c r="U15" s="10"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
       <c r="L16" s="15" t="s">
         <v>23</v>
       </c>
@@ -1501,24 +1508,24 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="18" t="s">
+      <c r="D17" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
+      <c r="F17" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
       <c r="L17" s="9" t="s">
         <v>0</v>
       </c>
@@ -1544,14 +1551,14 @@
       <c r="B18">
         <v>2</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
       <c r="L18" s="11" t="s">
         <v>5</v>
       </c>
@@ -1587,14 +1594,14 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C19" s="17"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
       <c r="L19" s="12" t="s">
         <v>15</v>
       </c>
@@ -1620,14 +1627,14 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C20" s="17"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
       <c r="L20" s="14" t="s">
         <v>17</v>
       </c>
@@ -1651,14 +1658,14 @@
       <c r="U20" s="10"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C21" s="17"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
       <c r="L21" s="15" t="s">
         <v>23</v>
       </c>
@@ -1677,24 +1684,24 @@
       <c r="U21" s="10"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="23"/>
-      <c r="F22" s="18" t="s">
+      <c r="D22" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="22"/>
+      <c r="F22" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J22" s="17"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="21"/>
       <c r="L22" s="9" t="s">
         <v>0</v>
       </c>
@@ -1717,14 +1724,14 @@
       <c r="U22" s="10"/>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="17"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="21"/>
       <c r="L23" s="11" t="s">
         <v>5</v>
       </c>
@@ -1760,14 +1767,14 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="17"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="21"/>
       <c r="L24" s="12" t="s">
         <v>15</v>
       </c>
@@ -1793,14 +1800,14 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="17"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="21"/>
       <c r="L25" s="14" t="s">
         <v>17</v>
       </c>
@@ -1823,14 +1830,14 @@
       <c r="U25" s="10"/>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="17"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="21"/>
       <c r="L26" s="15" t="s">
         <v>23</v>
       </c>
@@ -1859,26 +1866,26 @@
       <c r="B29" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F29" s="23"/>
-      <c r="G29" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I29" s="25" t="s">
+      <c r="E29" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" s="22"/>
+      <c r="G29" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="J29" s="17"/>
+      <c r="J29" s="21"/>
       <c r="L29" s="9" t="s">
         <v>0</v>
       </c>
@@ -1904,14 +1911,14 @@
       <c r="B30">
         <v>3</v>
       </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="17"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="21"/>
       <c r="L30" s="11" t="s">
         <v>5</v>
       </c>
@@ -1947,14 +1954,14 @@
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="17"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="21"/>
       <c r="L31" s="12" t="s">
         <v>15</v>
       </c>
@@ -1980,14 +1987,14 @@
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C32" s="17"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="17"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="21"/>
       <c r="L32" s="14" t="s">
         <v>17</v>
       </c>
@@ -2011,14 +2018,14 @@
       <c r="U32" s="10"/>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C33" s="17"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="17"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="21"/>
       <c r="L33" s="15" t="s">
         <v>23</v>
       </c>
@@ -2037,24 +2044,24 @@
       <c r="U33" s="10"/>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F34" s="23"/>
-      <c r="G34" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I34" s="18" t="s">
+      <c r="D34" s="21"/>
+      <c r="E34" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="22"/>
+      <c r="G34" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J34" s="22" t="s">
+      <c r="J34" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L34" s="9" t="s">
@@ -2079,14 +2086,14 @@
       <c r="U34" s="10"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="22"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="26"/>
       <c r="L35" s="11" t="s">
         <v>5</v>
       </c>
@@ -2125,14 +2132,14 @@
       <c r="A36">
         <v>5</v>
       </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="22"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="26"/>
       <c r="L36" s="12" t="s">
         <v>15</v>
       </c>
@@ -2158,14 +2165,14 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="22"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="26"/>
       <c r="L37" s="14" t="s">
         <v>17</v>
       </c>
@@ -2188,14 +2195,14 @@
       <c r="U37" s="10"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="22"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="26"/>
       <c r="L38" s="15" t="s">
         <v>23</v>
       </c>
@@ -2215,26 +2222,26 @@
       <c r="B39" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="18" t="s">
+      <c r="D39" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F39" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I39" s="17"/>
-      <c r="J39" s="27" t="s">
+      <c r="F39" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H39" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" s="21"/>
+      <c r="J39" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L39" s="9" t="s">
@@ -2262,14 +2269,14 @@
       <c r="B40">
         <v>4</v>
       </c>
-      <c r="C40" s="17"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="27"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="20"/>
       <c r="L40" s="11" t="s">
         <v>5</v>
       </c>
@@ -2308,14 +2315,14 @@
       <c r="B41" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="17"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="27"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="20"/>
       <c r="L41" s="12" t="s">
         <v>15</v>
       </c>
@@ -2344,14 +2351,14 @@
       <c r="B42">
         <v>0</v>
       </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="27"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="20"/>
       <c r="L42" s="14" t="s">
         <v>17</v>
       </c>
@@ -2376,14 +2383,14 @@
       <c r="U42" s="10"/>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C43" s="17"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="27"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="20"/>
       <c r="L43" s="15" t="s">
         <v>23</v>
       </c>
@@ -2404,26 +2411,26 @@
       <c r="U43" s="10"/>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D44" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E44" s="23"/>
-      <c r="F44" s="18" t="s">
+      <c r="D44" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="22"/>
+      <c r="F44" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G44" s="18" t="s">
+      <c r="G44" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H44" s="18" t="s">
+      <c r="H44" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I44" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J44" s="17"/>
+      <c r="I44" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J44" s="21"/>
       <c r="L44" s="9" t="s">
         <v>0</v>
       </c>
@@ -2446,14 +2453,14 @@
       <c r="U44" s="10"/>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="17"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="21"/>
       <c r="L45" s="11" t="s">
         <v>5</v>
       </c>
@@ -2489,14 +2496,14 @@
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="17"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="21"/>
       <c r="L46" s="12" t="s">
         <v>15</v>
       </c>
@@ -2522,14 +2529,14 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="17"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="21"/>
       <c r="L47" s="14" t="s">
         <v>17</v>
       </c>
@@ -2552,14 +2559,14 @@
       <c r="U47" s="10"/>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="22"/>
-      <c r="J48" s="17"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="25"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="21"/>
       <c r="L48" s="15" t="s">
         <v>23</v>
       </c>
@@ -2582,26 +2589,26 @@
       <c r="B50" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D50" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E50" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H50" s="17"/>
-      <c r="I50" s="25" t="s">
+      <c r="E50" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H50" s="21"/>
+      <c r="I50" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="J50" s="17"/>
+      <c r="J50" s="21"/>
       <c r="L50" s="9" t="s">
         <v>0</v>
       </c>
@@ -2627,14 +2634,14 @@
       <c r="B51">
         <v>5</v>
       </c>
-      <c r="C51" s="17"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="22"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="26"/>
-      <c r="J51" s="17"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="21"/>
       <c r="L51" s="11" t="s">
         <v>5</v>
       </c>
@@ -2670,14 +2677,14 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C52" s="17"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="17"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="21"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="21"/>
       <c r="L52" s="12" t="s">
         <v>15</v>
       </c>
@@ -2703,14 +2710,14 @@
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C53" s="17"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="17"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="21"/>
       <c r="L53" s="14" t="s">
         <v>17</v>
       </c>
@@ -2734,14 +2741,14 @@
       <c r="U53" s="10"/>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C54" s="17"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="17"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="21"/>
       <c r="L54" s="15" t="s">
         <v>23</v>
       </c>
@@ -2760,24 +2767,24 @@
       <c r="U54" s="10"/>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C55" s="17" t="s">
+      <c r="C55" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F55" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H55" s="17"/>
-      <c r="I55" s="18" t="s">
+      <c r="D55" s="21"/>
+      <c r="E55" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H55" s="21"/>
+      <c r="I55" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J55" s="22" t="s">
+      <c r="J55" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L55" s="9" t="s">
@@ -2802,14 +2809,14 @@
       <c r="U55" s="10"/>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="22"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="26"/>
       <c r="L56" s="11" t="s">
         <v>5</v>
       </c>
@@ -2845,14 +2852,14 @@
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="17"/>
-      <c r="I57" s="18"/>
-      <c r="J57" s="22"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="21"/>
+      <c r="G57" s="21"/>
+      <c r="H57" s="21"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="26"/>
       <c r="L57" s="12" t="s">
         <v>15</v>
       </c>
@@ -2878,14 +2885,14 @@
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C58" s="17"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="18"/>
-      <c r="J58" s="22"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="26"/>
       <c r="L58" s="14" t="s">
         <v>17</v>
       </c>
@@ -2908,14 +2915,14 @@
       <c r="U58" s="10"/>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C59" s="17"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="17"/>
-      <c r="G59" s="17"/>
-      <c r="H59" s="17"/>
-      <c r="I59" s="18"/>
-      <c r="J59" s="22"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="21"/>
+      <c r="H59" s="21"/>
+      <c r="I59" s="25"/>
+      <c r="J59" s="26"/>
       <c r="L59" s="15" t="s">
         <v>23</v>
       </c>
@@ -2935,26 +2942,26 @@
       <c r="B60" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D60" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E60" s="18" t="s">
+      <c r="D60" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F60" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H60" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I60" s="17"/>
-      <c r="J60" s="27" t="s">
+      <c r="F60" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H60" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I60" s="21"/>
+      <c r="J60" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L60" s="9" t="s">
@@ -2982,14 +2989,14 @@
       <c r="B61">
         <v>6</v>
       </c>
-      <c r="C61" s="17"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="18"/>
-      <c r="F61" s="17"/>
-      <c r="G61" s="17"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="17"/>
-      <c r="J61" s="27"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="21"/>
+      <c r="J61" s="20"/>
       <c r="L61" s="11" t="s">
         <v>5</v>
       </c>
@@ -3031,14 +3038,14 @@
       <c r="B62" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C62" s="17"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="18"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="27"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="21"/>
+      <c r="J62" s="20"/>
       <c r="L62" s="12" t="s">
         <v>15</v>
       </c>
@@ -3067,14 +3074,14 @@
       <c r="B63">
         <v>1</v>
       </c>
-      <c r="C63" s="17"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="27"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="21"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="21"/>
+      <c r="J63" s="20"/>
       <c r="L63" s="14" t="s">
         <v>17</v>
       </c>
@@ -3099,14 +3106,14 @@
       <c r="U63" s="10"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C64" s="17"/>
-      <c r="D64" s="23"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="17"/>
-      <c r="G64" s="17"/>
-      <c r="H64" s="22"/>
-      <c r="I64" s="17"/>
-      <c r="J64" s="27"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="21"/>
+      <c r="J64" s="20"/>
       <c r="L64" s="15" t="s">
         <v>23</v>
       </c>
@@ -3127,26 +3134,26 @@
       <c r="U64" s="10"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C65" s="17" t="s">
+      <c r="C65" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D65" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E65" s="23"/>
-      <c r="F65" s="18" t="s">
+      <c r="D65" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65" s="22"/>
+      <c r="F65" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G65" s="18" t="s">
+      <c r="G65" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H65" s="18" t="s">
+      <c r="H65" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I65" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J65" s="17"/>
+      <c r="I65" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J65" s="21"/>
       <c r="L65" s="9" t="s">
         <v>0</v>
       </c>
@@ -3169,14 +3176,14 @@
       <c r="U65" s="10"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C66" s="17"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="23"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="18"/>
-      <c r="I66" s="22"/>
-      <c r="J66" s="17"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="25"/>
+      <c r="I66" s="26"/>
+      <c r="J66" s="21"/>
       <c r="L66" s="11" t="s">
         <v>5</v>
       </c>
@@ -3212,14 +3219,14 @@
       </c>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="23"/>
-      <c r="F67" s="18"/>
-      <c r="G67" s="18"/>
-      <c r="H67" s="18"/>
-      <c r="I67" s="22"/>
-      <c r="J67" s="17"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="25"/>
+      <c r="G67" s="25"/>
+      <c r="H67" s="25"/>
+      <c r="I67" s="26"/>
+      <c r="J67" s="21"/>
       <c r="L67" s="12" t="s">
         <v>15</v>
       </c>
@@ -3245,14 +3252,14 @@
       </c>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C68" s="17"/>
-      <c r="D68" s="17"/>
-      <c r="E68" s="23"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="18"/>
-      <c r="H68" s="18"/>
-      <c r="I68" s="22"/>
-      <c r="J68" s="17"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="26"/>
+      <c r="J68" s="21"/>
       <c r="L68" s="14" t="s">
         <v>17</v>
       </c>
@@ -3275,14 +3282,14 @@
       <c r="U68" s="10"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C69" s="17"/>
-      <c r="D69" s="17"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="18"/>
-      <c r="G69" s="18"/>
-      <c r="H69" s="18"/>
-      <c r="I69" s="22"/>
-      <c r="J69" s="17"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="26"/>
+      <c r="J69" s="21"/>
       <c r="L69" s="15" t="s">
         <v>23</v>
       </c>
@@ -3305,36 +3312,36 @@
       <c r="P71" s="10"/>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="B72" s="28" t="s">
+      <c r="B72" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="C72" s="28"/>
+      <c r="C72" s="27"/>
       <c r="P72" s="10"/>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B73" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C73" s="17" t="s">
+      <c r="C73" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D73" s="18" t="s">
+      <c r="D73" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E73" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F73" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="22"/>
-      <c r="H73" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I73" s="25" t="s">
+      <c r="E73" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F73" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="26"/>
+      <c r="H73" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I73" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="J73" s="17"/>
+      <c r="J73" s="21"/>
       <c r="L73" s="9" t="s">
         <v>0</v>
       </c>
@@ -3360,14 +3367,14 @@
       <c r="B74">
         <v>7</v>
       </c>
-      <c r="C74" s="17"/>
-      <c r="D74" s="18"/>
-      <c r="E74" s="23"/>
-      <c r="F74" s="22"/>
-      <c r="G74" s="22"/>
-      <c r="H74" s="17"/>
-      <c r="I74" s="26"/>
-      <c r="J74" s="17"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="24"/>
+      <c r="J74" s="21"/>
       <c r="L74" s="11" t="s">
         <v>5</v>
       </c>
@@ -3403,14 +3410,14 @@
       </c>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C75" s="17"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="23"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="17"/>
-      <c r="I75" s="26"/>
-      <c r="J75" s="17"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="21"/>
+      <c r="I75" s="24"/>
+      <c r="J75" s="21"/>
       <c r="L75" s="12" t="s">
         <v>15</v>
       </c>
@@ -3436,14 +3443,14 @@
       </c>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C76" s="17"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="23"/>
-      <c r="F76" s="22"/>
-      <c r="G76" s="22"/>
-      <c r="H76" s="17"/>
-      <c r="I76" s="26"/>
-      <c r="J76" s="17"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="25"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="21"/>
+      <c r="I76" s="24"/>
+      <c r="J76" s="21"/>
       <c r="L76" s="14" t="s">
         <v>17</v>
       </c>
@@ -3467,14 +3474,14 @@
       <c r="U76" s="10"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C77" s="17"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="23"/>
-      <c r="F77" s="22"/>
-      <c r="G77" s="22"/>
-      <c r="H77" s="17"/>
-      <c r="I77" s="26"/>
-      <c r="J77" s="17"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="25"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="26"/>
+      <c r="H77" s="21"/>
+      <c r="I77" s="24"/>
+      <c r="J77" s="21"/>
       <c r="L77" s="15" t="s">
         <v>23</v>
       </c>
@@ -3493,24 +3500,24 @@
       <c r="U77" s="10"/>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C78" s="17" t="s">
+      <c r="C78" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D78" s="17"/>
-      <c r="E78" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F78" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="17"/>
-      <c r="H78" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I78" s="18" t="s">
+      <c r="D78" s="21"/>
+      <c r="E78" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F78" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="21"/>
+      <c r="H78" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I78" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J78" s="22" t="s">
+      <c r="J78" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L78" s="9" t="s">
@@ -3535,14 +3542,14 @@
       <c r="U78" s="10"/>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C79" s="17"/>
-      <c r="D79" s="17"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="17"/>
-      <c r="G79" s="17"/>
-      <c r="H79" s="17"/>
-      <c r="I79" s="18"/>
-      <c r="J79" s="22"/>
+      <c r="C79" s="21"/>
+      <c r="D79" s="21"/>
+      <c r="E79" s="21"/>
+      <c r="F79" s="21"/>
+      <c r="G79" s="21"/>
+      <c r="H79" s="21"/>
+      <c r="I79" s="25"/>
+      <c r="J79" s="26"/>
       <c r="L79" s="11" t="s">
         <v>5</v>
       </c>
@@ -3578,14 +3585,14 @@
       </c>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C80" s="17"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="17"/>
-      <c r="G80" s="17"/>
-      <c r="H80" s="17"/>
-      <c r="I80" s="18"/>
-      <c r="J80" s="22"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="21"/>
+      <c r="G80" s="21"/>
+      <c r="H80" s="21"/>
+      <c r="I80" s="25"/>
+      <c r="J80" s="26"/>
       <c r="L80" s="12" t="s">
         <v>15</v>
       </c>
@@ -3611,14 +3618,14 @@
       </c>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17"/>
-      <c r="G81" s="17"/>
-      <c r="H81" s="17"/>
-      <c r="I81" s="18"/>
-      <c r="J81" s="22"/>
+      <c r="C81" s="21"/>
+      <c r="D81" s="21"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="21"/>
+      <c r="G81" s="21"/>
+      <c r="H81" s="21"/>
+      <c r="I81" s="25"/>
+      <c r="J81" s="26"/>
       <c r="L81" s="14" t="s">
         <v>17</v>
       </c>
@@ -3641,14 +3648,14 @@
       <c r="U81" s="10"/>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C82" s="17"/>
-      <c r="D82" s="17"/>
-      <c r="E82" s="17"/>
-      <c r="F82" s="17"/>
-      <c r="G82" s="17"/>
-      <c r="H82" s="17"/>
-      <c r="I82" s="18"/>
-      <c r="J82" s="22"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="21"/>
+      <c r="H82" s="21"/>
+      <c r="I82" s="25"/>
+      <c r="J82" s="26"/>
       <c r="L82" s="15" t="s">
         <v>23</v>
       </c>
@@ -3665,24 +3672,24 @@
       <c r="U82" s="10"/>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C83" s="17" t="s">
+      <c r="C83" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D83" s="17"/>
-      <c r="E83" s="18" t="s">
+      <c r="D83" s="21"/>
+      <c r="E83" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F83" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="G83" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I83" s="17"/>
-      <c r="J83" s="27" t="s">
+      <c r="F83" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H83" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I83" s="21"/>
+      <c r="J83" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L83" s="9" t="s">
@@ -3707,14 +3714,14 @@
       <c r="U83" s="10"/>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="18"/>
-      <c r="F84" s="30"/>
-      <c r="G84" s="22"/>
-      <c r="H84" s="30"/>
-      <c r="I84" s="17"/>
-      <c r="J84" s="27"/>
+      <c r="C84" s="21"/>
+      <c r="D84" s="21"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="26"/>
+      <c r="H84" s="18"/>
+      <c r="I84" s="21"/>
+      <c r="J84" s="20"/>
       <c r="L84" s="11" t="s">
         <v>5</v>
       </c>
@@ -3753,14 +3760,14 @@
       <c r="B85" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C85" s="17"/>
-      <c r="D85" s="17"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="30"/>
-      <c r="G85" s="22"/>
-      <c r="H85" s="30"/>
-      <c r="I85" s="17"/>
-      <c r="J85" s="27"/>
+      <c r="C85" s="21"/>
+      <c r="D85" s="21"/>
+      <c r="E85" s="25"/>
+      <c r="F85" s="18"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="18"/>
+      <c r="I85" s="21"/>
+      <c r="J85" s="20"/>
       <c r="L85" s="12" t="s">
         <v>15</v>
       </c>
@@ -3789,14 +3796,14 @@
       <c r="B86">
         <v>2</v>
       </c>
-      <c r="C86" s="17"/>
-      <c r="D86" s="17"/>
-      <c r="E86" s="18"/>
-      <c r="F86" s="30"/>
-      <c r="G86" s="22"/>
-      <c r="H86" s="30"/>
-      <c r="I86" s="17"/>
-      <c r="J86" s="27"/>
+      <c r="C86" s="21"/>
+      <c r="D86" s="21"/>
+      <c r="E86" s="25"/>
+      <c r="F86" s="18"/>
+      <c r="G86" s="26"/>
+      <c r="H86" s="18"/>
+      <c r="I86" s="21"/>
+      <c r="J86" s="20"/>
       <c r="L86" s="14" t="s">
         <v>17</v>
       </c>
@@ -3820,14 +3827,14 @@
       <c r="U86" s="10"/>
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C87" s="17"/>
-      <c r="D87" s="17"/>
-      <c r="E87" s="18"/>
-      <c r="F87" s="31"/>
-      <c r="G87" s="22"/>
-      <c r="H87" s="31"/>
-      <c r="I87" s="17"/>
-      <c r="J87" s="27"/>
+      <c r="C87" s="21"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="25"/>
+      <c r="F87" s="19"/>
+      <c r="G87" s="26"/>
+      <c r="H87" s="19"/>
+      <c r="I87" s="21"/>
+      <c r="J87" s="20"/>
       <c r="L87" s="15" t="s">
         <v>23</v>
       </c>
@@ -3846,24 +3853,24 @@
       <c r="U87" s="10"/>
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C88" s="17" t="s">
+      <c r="C88" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D88" s="17"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="18" t="s">
+      <c r="D88" s="21"/>
+      <c r="E88" s="22"/>
+      <c r="F88" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G88" s="18" t="s">
+      <c r="G88" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H88" s="18" t="s">
+      <c r="H88" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I88" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J88" s="17"/>
+      <c r="I88" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J88" s="21"/>
       <c r="L88" s="9" t="s">
         <v>0</v>
       </c>
@@ -3886,14 +3893,14 @@
       <c r="U88" s="10"/>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C89" s="17"/>
-      <c r="D89" s="17"/>
-      <c r="E89" s="23"/>
-      <c r="F89" s="18"/>
-      <c r="G89" s="18"/>
-      <c r="H89" s="18"/>
-      <c r="I89" s="22"/>
-      <c r="J89" s="17"/>
+      <c r="C89" s="21"/>
+      <c r="D89" s="21"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="25"/>
+      <c r="G89" s="25"/>
+      <c r="H89" s="25"/>
+      <c r="I89" s="26"/>
+      <c r="J89" s="21"/>
       <c r="L89" s="11" t="s">
         <v>5</v>
       </c>
@@ -3932,14 +3939,14 @@
       <c r="A90">
         <v>15</v>
       </c>
-      <c r="C90" s="17"/>
-      <c r="D90" s="17"/>
-      <c r="E90" s="23"/>
-      <c r="F90" s="18"/>
-      <c r="G90" s="18"/>
-      <c r="H90" s="18"/>
-      <c r="I90" s="22"/>
-      <c r="J90" s="17"/>
+      <c r="C90" s="21"/>
+      <c r="D90" s="21"/>
+      <c r="E90" s="22"/>
+      <c r="F90" s="25"/>
+      <c r="G90" s="25"/>
+      <c r="H90" s="25"/>
+      <c r="I90" s="26"/>
+      <c r="J90" s="21"/>
       <c r="L90" s="12" t="s">
         <v>15</v>
       </c>
@@ -3965,14 +3972,14 @@
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C91" s="17"/>
-      <c r="D91" s="17"/>
-      <c r="E91" s="23"/>
-      <c r="F91" s="18"/>
-      <c r="G91" s="18"/>
-      <c r="H91" s="18"/>
-      <c r="I91" s="22"/>
-      <c r="J91" s="17"/>
+      <c r="C91" s="21"/>
+      <c r="D91" s="21"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="25"/>
+      <c r="G91" s="25"/>
+      <c r="H91" s="25"/>
+      <c r="I91" s="26"/>
+      <c r="J91" s="21"/>
       <c r="L91" s="14" t="s">
         <v>17</v>
       </c>
@@ -3995,14 +4002,14 @@
       <c r="U91" s="10"/>
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C92" s="17"/>
-      <c r="D92" s="17"/>
-      <c r="E92" s="23"/>
-      <c r="F92" s="18"/>
-      <c r="G92" s="18"/>
-      <c r="H92" s="18"/>
-      <c r="I92" s="22"/>
-      <c r="J92" s="17"/>
+      <c r="C92" s="21"/>
+      <c r="D92" s="21"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="25"/>
+      <c r="G92" s="25"/>
+      <c r="H92" s="25"/>
+      <c r="I92" s="26"/>
+      <c r="J92" s="21"/>
       <c r="L92" s="15" t="s">
         <v>23</v>
       </c>
@@ -4022,18 +4029,18 @@
       <c r="P93" s="10"/>
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C94" s="17" t="s">
+      <c r="C94" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="D94" s="17"/>
-      <c r="E94" s="23"/>
-      <c r="F94" s="23"/>
-      <c r="G94" s="17"/>
-      <c r="H94" s="17"/>
-      <c r="I94" s="25" t="s">
+      <c r="D94" s="21"/>
+      <c r="E94" s="22"/>
+      <c r="F94" s="22"/>
+      <c r="G94" s="21"/>
+      <c r="H94" s="21"/>
+      <c r="I94" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="J94" s="17"/>
+      <c r="J94" s="21"/>
       <c r="L94" s="9" t="s">
         <v>0</v>
       </c>
@@ -4056,14 +4063,14 @@
       <c r="U94" s="10"/>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C95" s="17"/>
-      <c r="D95" s="17"/>
-      <c r="E95" s="23"/>
-      <c r="F95" s="23"/>
-      <c r="G95" s="17"/>
-      <c r="H95" s="17"/>
-      <c r="I95" s="26"/>
-      <c r="J95" s="17"/>
+      <c r="C95" s="21"/>
+      <c r="D95" s="21"/>
+      <c r="E95" s="22"/>
+      <c r="F95" s="22"/>
+      <c r="G95" s="21"/>
+      <c r="H95" s="21"/>
+      <c r="I95" s="24"/>
+      <c r="J95" s="21"/>
       <c r="L95" s="11" t="s">
         <v>5</v>
       </c>
@@ -4099,14 +4106,14 @@
       </c>
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C96" s="17"/>
-      <c r="D96" s="17"/>
-      <c r="E96" s="23"/>
-      <c r="F96" s="23"/>
-      <c r="G96" s="17"/>
-      <c r="H96" s="17"/>
-      <c r="I96" s="26"/>
-      <c r="J96" s="17"/>
+      <c r="C96" s="21"/>
+      <c r="D96" s="21"/>
+      <c r="E96" s="22"/>
+      <c r="F96" s="22"/>
+      <c r="G96" s="21"/>
+      <c r="H96" s="21"/>
+      <c r="I96" s="24"/>
+      <c r="J96" s="21"/>
       <c r="L96" s="12" t="s">
         <v>15</v>
       </c>
@@ -4124,14 +4131,14 @@
       <c r="V96" s="10"/>
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C97" s="17"/>
-      <c r="D97" s="17"/>
-      <c r="E97" s="23"/>
-      <c r="F97" s="23"/>
-      <c r="G97" s="17"/>
-      <c r="H97" s="17"/>
-      <c r="I97" s="26"/>
-      <c r="J97" s="17"/>
+      <c r="C97" s="21"/>
+      <c r="D97" s="21"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="22"/>
+      <c r="G97" s="21"/>
+      <c r="H97" s="21"/>
+      <c r="I97" s="24"/>
+      <c r="J97" s="21"/>
       <c r="L97" s="14" t="s">
         <v>17</v>
       </c>
@@ -4154,14 +4161,14 @@
       <c r="U97" s="10"/>
     </row>
     <row r="98" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C98" s="17"/>
-      <c r="D98" s="17"/>
-      <c r="E98" s="23"/>
-      <c r="F98" s="23"/>
-      <c r="G98" s="17"/>
-      <c r="H98" s="17"/>
-      <c r="I98" s="26"/>
-      <c r="J98" s="17"/>
+      <c r="C98" s="21"/>
+      <c r="D98" s="21"/>
+      <c r="E98" s="22"/>
+      <c r="F98" s="22"/>
+      <c r="G98" s="21"/>
+      <c r="H98" s="21"/>
+      <c r="I98" s="24"/>
+      <c r="J98" s="21"/>
       <c r="L98" s="15" t="s">
         <v>23</v>
       </c>
@@ -4178,18 +4185,18 @@
       <c r="U98" s="10"/>
     </row>
     <row r="99" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C99" s="17" t="s">
+      <c r="C99" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D99" s="17"/>
-      <c r="E99" s="23"/>
-      <c r="F99" s="23"/>
-      <c r="G99" s="17"/>
-      <c r="H99" s="17"/>
-      <c r="I99" s="18" t="s">
+      <c r="D99" s="21"/>
+      <c r="E99" s="22"/>
+      <c r="F99" s="22"/>
+      <c r="G99" s="21"/>
+      <c r="H99" s="21"/>
+      <c r="I99" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J99" s="22" t="s">
+      <c r="J99" s="26" t="s">
         <v>26</v>
       </c>
       <c r="L99" s="9" t="s">
@@ -4214,14 +4221,14 @@
       <c r="U99" s="10"/>
     </row>
     <row r="100" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C100" s="17"/>
-      <c r="D100" s="17"/>
-      <c r="E100" s="23"/>
-      <c r="F100" s="23"/>
-      <c r="G100" s="17"/>
-      <c r="H100" s="17"/>
-      <c r="I100" s="18"/>
-      <c r="J100" s="22"/>
+      <c r="C100" s="21"/>
+      <c r="D100" s="21"/>
+      <c r="E100" s="22"/>
+      <c r="F100" s="22"/>
+      <c r="G100" s="21"/>
+      <c r="H100" s="21"/>
+      <c r="I100" s="25"/>
+      <c r="J100" s="26"/>
       <c r="L100" s="11" t="s">
         <v>5</v>
       </c>
@@ -4257,14 +4264,14 @@
       </c>
     </row>
     <row r="101" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C101" s="17"/>
-      <c r="D101" s="17"/>
-      <c r="E101" s="23"/>
-      <c r="F101" s="23"/>
-      <c r="G101" s="17"/>
-      <c r="H101" s="17"/>
-      <c r="I101" s="18"/>
-      <c r="J101" s="22"/>
+      <c r="C101" s="21"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="22"/>
+      <c r="F101" s="22"/>
+      <c r="G101" s="21"/>
+      <c r="H101" s="21"/>
+      <c r="I101" s="25"/>
+      <c r="J101" s="26"/>
       <c r="L101" s="12" t="s">
         <v>15</v>
       </c>
@@ -4290,14 +4297,14 @@
       </c>
     </row>
     <row r="102" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C102" s="17"/>
-      <c r="D102" s="17"/>
-      <c r="E102" s="23"/>
-      <c r="F102" s="23"/>
-      <c r="G102" s="17"/>
-      <c r="H102" s="17"/>
-      <c r="I102" s="18"/>
-      <c r="J102" s="22"/>
+      <c r="C102" s="21"/>
+      <c r="D102" s="21"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="21"/>
+      <c r="H102" s="21"/>
+      <c r="I102" s="25"/>
+      <c r="J102" s="26"/>
       <c r="L102" s="14" t="s">
         <v>17</v>
       </c>
@@ -4320,14 +4327,14 @@
       <c r="U102" s="10"/>
     </row>
     <row r="103" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C103" s="17"/>
-      <c r="D103" s="17"/>
-      <c r="E103" s="23"/>
-      <c r="F103" s="23"/>
-      <c r="G103" s="17"/>
-      <c r="H103" s="17"/>
-      <c r="I103" s="18"/>
-      <c r="J103" s="22"/>
+      <c r="C103" s="21"/>
+      <c r="D103" s="21"/>
+      <c r="E103" s="22"/>
+      <c r="F103" s="22"/>
+      <c r="G103" s="21"/>
+      <c r="H103" s="21"/>
+      <c r="I103" s="25"/>
+      <c r="J103" s="26"/>
       <c r="L103" s="15" t="s">
         <v>23</v>
       </c>
@@ -4344,16 +4351,16 @@
       <c r="U103" s="10"/>
     </row>
     <row r="104" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C104" s="17" t="s">
+      <c r="C104" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D104" s="17"/>
-      <c r="E104" s="23"/>
-      <c r="F104" s="23"/>
-      <c r="G104" s="17"/>
-      <c r="H104" s="17"/>
-      <c r="I104" s="29"/>
-      <c r="J104" s="27" t="s">
+      <c r="D104" s="21"/>
+      <c r="E104" s="22"/>
+      <c r="F104" s="22"/>
+      <c r="G104" s="21"/>
+      <c r="H104" s="21"/>
+      <c r="I104" s="17"/>
+      <c r="J104" s="20" t="s">
         <v>33</v>
       </c>
       <c r="L104" s="9" t="s">
@@ -4378,14 +4385,14 @@
       <c r="U104" s="10"/>
     </row>
     <row r="105" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C105" s="17"/>
-      <c r="D105" s="17"/>
-      <c r="E105" s="23"/>
-      <c r="F105" s="23"/>
-      <c r="G105" s="17"/>
-      <c r="H105" s="17"/>
-      <c r="I105" s="30"/>
-      <c r="J105" s="27"/>
+      <c r="C105" s="21"/>
+      <c r="D105" s="21"/>
+      <c r="E105" s="22"/>
+      <c r="F105" s="22"/>
+      <c r="G105" s="21"/>
+      <c r="H105" s="21"/>
+      <c r="I105" s="18"/>
+      <c r="J105" s="20"/>
       <c r="L105" s="11" t="s">
         <v>5</v>
       </c>
@@ -4427,14 +4434,14 @@
       <c r="B106" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C106" s="17"/>
-      <c r="D106" s="17"/>
-      <c r="E106" s="23"/>
-      <c r="F106" s="23"/>
-      <c r="G106" s="17"/>
-      <c r="H106" s="17"/>
-      <c r="I106" s="30"/>
-      <c r="J106" s="27"/>
+      <c r="C106" s="21"/>
+      <c r="D106" s="21"/>
+      <c r="E106" s="22"/>
+      <c r="F106" s="22"/>
+      <c r="G106" s="21"/>
+      <c r="H106" s="21"/>
+      <c r="I106" s="18"/>
+      <c r="J106" s="20"/>
       <c r="L106" s="12" t="s">
         <v>15</v>
       </c>
@@ -4455,14 +4462,14 @@
       <c r="B107">
         <v>3</v>
       </c>
-      <c r="C107" s="17"/>
-      <c r="D107" s="17"/>
-      <c r="E107" s="23"/>
-      <c r="F107" s="23"/>
-      <c r="G107" s="17"/>
-      <c r="H107" s="17"/>
-      <c r="I107" s="30"/>
-      <c r="J107" s="27"/>
+      <c r="C107" s="21"/>
+      <c r="D107" s="21"/>
+      <c r="E107" s="22"/>
+      <c r="F107" s="22"/>
+      <c r="G107" s="21"/>
+      <c r="H107" s="21"/>
+      <c r="I107" s="18"/>
+      <c r="J107" s="20"/>
       <c r="L107" s="14" t="s">
         <v>17</v>
       </c>
@@ -4486,14 +4493,14 @@
       <c r="U107" s="10"/>
     </row>
     <row r="108" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C108" s="17"/>
-      <c r="D108" s="17"/>
-      <c r="E108" s="23"/>
-      <c r="F108" s="23"/>
-      <c r="G108" s="17"/>
-      <c r="H108" s="17"/>
-      <c r="I108" s="31"/>
-      <c r="J108" s="27"/>
+      <c r="C108" s="21"/>
+      <c r="D108" s="21"/>
+      <c r="E108" s="22"/>
+      <c r="F108" s="22"/>
+      <c r="G108" s="21"/>
+      <c r="H108" s="21"/>
+      <c r="I108" s="19"/>
+      <c r="J108" s="20"/>
       <c r="L108" s="15" t="s">
         <v>23</v>
       </c>
@@ -4512,6 +4519,135 @@
     </row>
   </sheetData>
   <mergeCells count="153">
+    <mergeCell ref="I7:I11"/>
+    <mergeCell ref="J7:J11"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="D12:D16"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="F12:F16"/>
+    <mergeCell ref="G12:G16"/>
+    <mergeCell ref="H12:H16"/>
+    <mergeCell ref="I12:I16"/>
+    <mergeCell ref="J12:J16"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="G7:G11"/>
+    <mergeCell ref="H7:H11"/>
+    <mergeCell ref="I17:I21"/>
+    <mergeCell ref="J17:J21"/>
+    <mergeCell ref="C22:C26"/>
+    <mergeCell ref="D22:D26"/>
+    <mergeCell ref="E22:E26"/>
+    <mergeCell ref="F22:F26"/>
+    <mergeCell ref="G22:G26"/>
+    <mergeCell ref="H22:H26"/>
+    <mergeCell ref="I22:I26"/>
+    <mergeCell ref="J22:J26"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="E17:E21"/>
+    <mergeCell ref="F17:F21"/>
+    <mergeCell ref="G17:G21"/>
+    <mergeCell ref="H17:H21"/>
+    <mergeCell ref="I29:I33"/>
+    <mergeCell ref="J29:J33"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="E34:E38"/>
+    <mergeCell ref="F34:F38"/>
+    <mergeCell ref="G34:G38"/>
+    <mergeCell ref="H34:H38"/>
+    <mergeCell ref="I34:I38"/>
+    <mergeCell ref="J34:J38"/>
+    <mergeCell ref="C29:C33"/>
+    <mergeCell ref="D29:D33"/>
+    <mergeCell ref="E29:E33"/>
+    <mergeCell ref="F29:F33"/>
+    <mergeCell ref="G29:G33"/>
+    <mergeCell ref="H29:H33"/>
+    <mergeCell ref="I39:I43"/>
+    <mergeCell ref="J39:J43"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="D44:D48"/>
+    <mergeCell ref="E44:E48"/>
+    <mergeCell ref="F44:F48"/>
+    <mergeCell ref="G44:G48"/>
+    <mergeCell ref="H44:H48"/>
+    <mergeCell ref="I44:I48"/>
+    <mergeCell ref="J44:J48"/>
+    <mergeCell ref="C39:C43"/>
+    <mergeCell ref="D39:D43"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="F39:F43"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="H39:H43"/>
+    <mergeCell ref="I50:I54"/>
+    <mergeCell ref="J50:J54"/>
+    <mergeCell ref="C55:C59"/>
+    <mergeCell ref="D55:D59"/>
+    <mergeCell ref="E55:E59"/>
+    <mergeCell ref="F55:F59"/>
+    <mergeCell ref="G55:G59"/>
+    <mergeCell ref="H55:H59"/>
+    <mergeCell ref="I55:I59"/>
+    <mergeCell ref="J55:J59"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="D50:D54"/>
+    <mergeCell ref="E50:E54"/>
+    <mergeCell ref="F50:F54"/>
+    <mergeCell ref="G50:G54"/>
+    <mergeCell ref="H50:H54"/>
+    <mergeCell ref="I60:I64"/>
+    <mergeCell ref="J60:J64"/>
+    <mergeCell ref="C65:C69"/>
+    <mergeCell ref="D65:D69"/>
+    <mergeCell ref="E65:E69"/>
+    <mergeCell ref="F65:F69"/>
+    <mergeCell ref="G65:G69"/>
+    <mergeCell ref="H65:H69"/>
+    <mergeCell ref="I65:I69"/>
+    <mergeCell ref="J65:J69"/>
+    <mergeCell ref="C60:C64"/>
+    <mergeCell ref="D60:D64"/>
+    <mergeCell ref="E60:E64"/>
+    <mergeCell ref="F60:F64"/>
+    <mergeCell ref="G60:G64"/>
+    <mergeCell ref="H60:H64"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="I73:I77"/>
+    <mergeCell ref="J73:J77"/>
+    <mergeCell ref="C78:C82"/>
+    <mergeCell ref="D78:D82"/>
+    <mergeCell ref="E78:E82"/>
+    <mergeCell ref="F78:F82"/>
+    <mergeCell ref="G78:G82"/>
+    <mergeCell ref="H78:H82"/>
+    <mergeCell ref="I78:I82"/>
+    <mergeCell ref="J78:J82"/>
+    <mergeCell ref="C73:C77"/>
+    <mergeCell ref="D73:D77"/>
+    <mergeCell ref="E73:E77"/>
+    <mergeCell ref="F73:F77"/>
+    <mergeCell ref="G73:G77"/>
+    <mergeCell ref="H73:H77"/>
+    <mergeCell ref="I83:I87"/>
+    <mergeCell ref="J83:J87"/>
+    <mergeCell ref="C88:C92"/>
+    <mergeCell ref="D88:D92"/>
+    <mergeCell ref="E88:E92"/>
+    <mergeCell ref="F88:F92"/>
+    <mergeCell ref="G88:G92"/>
+    <mergeCell ref="H88:H92"/>
+    <mergeCell ref="I88:I92"/>
+    <mergeCell ref="J88:J92"/>
+    <mergeCell ref="C83:C87"/>
+    <mergeCell ref="D83:D87"/>
+    <mergeCell ref="E83:E87"/>
+    <mergeCell ref="F83:F87"/>
+    <mergeCell ref="G83:G87"/>
+    <mergeCell ref="H83:H87"/>
     <mergeCell ref="I104:I108"/>
     <mergeCell ref="J104:J108"/>
     <mergeCell ref="C104:C108"/>
@@ -4536,135 +4672,6 @@
     <mergeCell ref="F94:F98"/>
     <mergeCell ref="G94:G98"/>
     <mergeCell ref="H94:H98"/>
-    <mergeCell ref="I83:I87"/>
-    <mergeCell ref="J83:J87"/>
-    <mergeCell ref="C88:C92"/>
-    <mergeCell ref="D88:D92"/>
-    <mergeCell ref="E88:E92"/>
-    <mergeCell ref="F88:F92"/>
-    <mergeCell ref="G88:G92"/>
-    <mergeCell ref="H88:H92"/>
-    <mergeCell ref="I88:I92"/>
-    <mergeCell ref="J88:J92"/>
-    <mergeCell ref="C83:C87"/>
-    <mergeCell ref="D83:D87"/>
-    <mergeCell ref="E83:E87"/>
-    <mergeCell ref="F83:F87"/>
-    <mergeCell ref="G83:G87"/>
-    <mergeCell ref="H83:H87"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="I73:I77"/>
-    <mergeCell ref="J73:J77"/>
-    <mergeCell ref="C78:C82"/>
-    <mergeCell ref="D78:D82"/>
-    <mergeCell ref="E78:E82"/>
-    <mergeCell ref="F78:F82"/>
-    <mergeCell ref="G78:G82"/>
-    <mergeCell ref="H78:H82"/>
-    <mergeCell ref="I78:I82"/>
-    <mergeCell ref="J78:J82"/>
-    <mergeCell ref="C73:C77"/>
-    <mergeCell ref="D73:D77"/>
-    <mergeCell ref="E73:E77"/>
-    <mergeCell ref="F73:F77"/>
-    <mergeCell ref="G73:G77"/>
-    <mergeCell ref="H73:H77"/>
-    <mergeCell ref="I60:I64"/>
-    <mergeCell ref="J60:J64"/>
-    <mergeCell ref="C65:C69"/>
-    <mergeCell ref="D65:D69"/>
-    <mergeCell ref="E65:E69"/>
-    <mergeCell ref="F65:F69"/>
-    <mergeCell ref="G65:G69"/>
-    <mergeCell ref="H65:H69"/>
-    <mergeCell ref="I65:I69"/>
-    <mergeCell ref="J65:J69"/>
-    <mergeCell ref="C60:C64"/>
-    <mergeCell ref="D60:D64"/>
-    <mergeCell ref="E60:E64"/>
-    <mergeCell ref="F60:F64"/>
-    <mergeCell ref="G60:G64"/>
-    <mergeCell ref="H60:H64"/>
-    <mergeCell ref="I50:I54"/>
-    <mergeCell ref="J50:J54"/>
-    <mergeCell ref="C55:C59"/>
-    <mergeCell ref="D55:D59"/>
-    <mergeCell ref="E55:E59"/>
-    <mergeCell ref="F55:F59"/>
-    <mergeCell ref="G55:G59"/>
-    <mergeCell ref="H55:H59"/>
-    <mergeCell ref="I55:I59"/>
-    <mergeCell ref="J55:J59"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="D50:D54"/>
-    <mergeCell ref="E50:E54"/>
-    <mergeCell ref="F50:F54"/>
-    <mergeCell ref="G50:G54"/>
-    <mergeCell ref="H50:H54"/>
-    <mergeCell ref="I39:I43"/>
-    <mergeCell ref="J39:J43"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="D44:D48"/>
-    <mergeCell ref="E44:E48"/>
-    <mergeCell ref="F44:F48"/>
-    <mergeCell ref="G44:G48"/>
-    <mergeCell ref="H44:H48"/>
-    <mergeCell ref="I44:I48"/>
-    <mergeCell ref="J44:J48"/>
-    <mergeCell ref="C39:C43"/>
-    <mergeCell ref="D39:D43"/>
-    <mergeCell ref="E39:E43"/>
-    <mergeCell ref="F39:F43"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="H39:H43"/>
-    <mergeCell ref="I29:I33"/>
-    <mergeCell ref="J29:J33"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D38"/>
-    <mergeCell ref="E34:E38"/>
-    <mergeCell ref="F34:F38"/>
-    <mergeCell ref="G34:G38"/>
-    <mergeCell ref="H34:H38"/>
-    <mergeCell ref="I34:I38"/>
-    <mergeCell ref="J34:J38"/>
-    <mergeCell ref="C29:C33"/>
-    <mergeCell ref="D29:D33"/>
-    <mergeCell ref="E29:E33"/>
-    <mergeCell ref="F29:F33"/>
-    <mergeCell ref="G29:G33"/>
-    <mergeCell ref="H29:H33"/>
-    <mergeCell ref="I17:I21"/>
-    <mergeCell ref="J17:J21"/>
-    <mergeCell ref="C22:C26"/>
-    <mergeCell ref="D22:D26"/>
-    <mergeCell ref="E22:E26"/>
-    <mergeCell ref="F22:F26"/>
-    <mergeCell ref="G22:G26"/>
-    <mergeCell ref="H22:H26"/>
-    <mergeCell ref="I22:I26"/>
-    <mergeCell ref="J22:J26"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="D17:D21"/>
-    <mergeCell ref="E17:E21"/>
-    <mergeCell ref="F17:F21"/>
-    <mergeCell ref="G17:G21"/>
-    <mergeCell ref="H17:H21"/>
-    <mergeCell ref="I7:I11"/>
-    <mergeCell ref="J7:J11"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="D12:D16"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="F12:F16"/>
-    <mergeCell ref="G12:G16"/>
-    <mergeCell ref="H12:H16"/>
-    <mergeCell ref="I12:I16"/>
-    <mergeCell ref="J12:J16"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="F7:F11"/>
-    <mergeCell ref="G7:G11"/>
-    <mergeCell ref="H7:H11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
